--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488005_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488005_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2785</v>
+        <v>3.3576</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1057</v>
+        <v>2.5414</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1727</v>
+        <v>0.8162</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1713</v>
+        <v>2.4124</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1905</v>
+        <v>2.9233</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0192</v>
+        <v>-0.5109</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8786</v>
+        <v>2.3721</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2358</v>
+        <v>2.3683</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6428</v>
+        <v>0.0039</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2927</v>
+        <v>0.0403</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9547</v>
+        <v>0.5551</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.662</v>
+        <v>-0.5148</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3758</v>
+        <v>0.0156</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2886</v>
+        <v>-0.3816</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0872</v>
+        <v>0.3972</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0704</v>
+        <v>0.5331</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0704</v>
+        <v>1.7403</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0862</v>
+        <v>2.2223</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3542</v>
+        <v>0.2742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7319</v>
+        <v>1.9481</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4124</v>
+        <v>1.1713</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9233</v>
+        <v>1.1905</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5109</v>
+        <v>-0.0192</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3721</v>
+        <v>0.8786</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3683</v>
+        <v>0.2358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0039</v>
+        <v>0.6428</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0403</v>
+        <v>0.2927</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5551</v>
+        <v>0.9547</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5148</v>
+        <v>-0.662</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2558</v>
+        <v>1.3196</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5688</v>
+        <v>0.4571</v>
       </c>
       <c r="U3" t="n">
-        <v>0.313</v>
+        <v>0.8625</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5331</v>
+        <v>-0.0704</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7403</v>
+        <v>-0.0704</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1366</v>
+        <v>1.3934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1887</v>
+        <v>0.642</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9479</v>
+        <v>0.7514</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3762</v>
@@ -844,13 +844,13 @@
         <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4871</v>
+        <v>-0.2304</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.068</v>
+        <v>-0.6147</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5808</v>
+        <v>0.3843</v>
       </c>
       <c r="V5" t="n">
         <v>2.4142</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6047</v>
+        <v>-0.3261</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2714</v>
+        <v>-1.8805</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6667</v>
+        <v>1.5543</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6516</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3729</v>
+        <v>0.6516</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>0.3213</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4426</v>
+        <v>0.3303</v>
       </c>
       <c r="V6" t="n">
         <v>0.674</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9914</v>
+        <v>-2.1599</v>
       </c>
       <c r="E7" t="n">
         <v>-2.0375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0461</v>
+        <v>-0.1224</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8057</v>
@@ -1000,13 +1000,13 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8054</v>
+        <v>0.6369</v>
       </c>
       <c r="T7" t="n">
         <v>0.4295</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3758</v>
+        <v>0.2074</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4145</v>
+        <v>-2.868</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6937</v>
+        <v>-1.5294</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7208</v>
+        <v>-1.3385</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1235</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.48</v>
+        <v>0.0265</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1232</v>
+        <v>-0.9589</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6032</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-3.7621</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4934</v>
+        <v>-3.9422</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0819</v>
+        <v>-2.8733</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4115</v>
+        <v>-1.0689</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5121</v>
+        <v>-3.1888</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6334</v>
+        <v>-0.1467</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8788</v>
+        <v>-3.0421</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.654</v>
+        <v>-0.8205</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9749</v>
+        <v>0.377</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6791</v>
+        <v>-1.1975</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8581</v>
+        <v>-2.3682</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3415</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1996</v>
+        <v>-1.8446</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0187</v>
+        <v>-0.9516</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4368</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4555</v>
+        <v>-0.0883</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.801</v>
+        <v>-3.9954</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5074</v>
+        <v>-2.612</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2936</v>
+        <v>-1.3834</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1888</v>
+        <v>-2.5121</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1467</v>
+        <v>-0.6334</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0421</v>
+        <v>-1.8788</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8205</v>
+        <v>-1.654</v>
       </c>
       <c r="K10" t="n">
-        <v>0.377</v>
+        <v>-0.9749</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1975</v>
+        <v>-0.6791</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3682</v>
+        <v>-0.8581</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.3415</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8446</v>
+        <v>-1.1996</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.7929</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.1982</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1893</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3876</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.8104</v>
+        <v>0.5167</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4975</v>
+        <v>0.0331</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3129</v>
+        <v>0.4836</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8057</v>
+        <v>-4.9394</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0157</v>
+        <v>-5.6829</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>0.7435</v>
       </c>
       <c r="G11" t="n">
         <v>-4.109</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3269</v>
+        <v>-0.4607</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2279</v>
+        <v>-0.4394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5548</v>
+        <v>-0.0213</v>
       </c>
       <c r="V11" t="n">
         <v>1.8107</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6786</v>
+        <v>-5.4704</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0374</v>
+        <v>-3.2784</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6412</v>
+        <v>-2.1919</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7301</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7413</v>
+        <v>-0.5331</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6223</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.119</v>
+        <v>0.3303</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.7773</v>
+        <v>-15.2174</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.4857</v>
+        <v>-14.9257</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2917999999999998</v>
+        <v>-0.2916000000000003</v>
       </c>
       <c r="G13" t="n">
         <v>-14.4026</v>
@@ -1444,7 +1444,7 @@
         <v>-4.024699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8715000000000002</v>
+        <v>0.8715000000000003</v>
       </c>
       <c r="L13" t="n">
         <v>-4.8964</v>
@@ -1459,7 +1459,7 @@
         <v>-12.5329</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9911999999999999</v>
+        <v>-0.9911999999999996</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.8932</v>
@@ -1468,10 +1468,10 @@
         <v>10.9022</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5686999999999998</v>
+        <v>0.9911</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.4402</v>
+        <v>-2.8804</v>
       </c>
       <c r="U13" t="n">
         <v>3.8714</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2954</v>
+        <v>5.8317</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0289</v>
+        <v>3.6214</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2665</v>
+        <v>2.2104</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4179</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2988</v>
+        <v>0.8351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0034</v>
+        <v>-0.4109</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3022</v>
+        <v>1.246</v>
       </c>
       <c r="V14" t="n">
         <v>3.234</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4377</v>
+        <v>4.0936</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5967</v>
+        <v>0.393</v>
       </c>
       <c r="F15" t="n">
-        <v>3.841</v>
+        <v>3.7006</v>
       </c>
       <c r="G15" t="n">
         <v>2.9724</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0003</v>
+        <v>0.6561</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3154</v>
+        <v>-0.5192</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3157</v>
+        <v>1.1753</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7243000000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2683</v>
+        <v>2.3003</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9424</v>
+        <v>-1.4331</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2107</v>
+        <v>3.7334</v>
       </c>
       <c r="G17" t="n">
         <v>2.1337</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2817</v>
+        <v>-0.2497</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1121</v>
+        <v>-0.6028</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8304</v>
+        <v>0.3531</v>
       </c>
       <c r="V17" t="n">
         <v>1.0109</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7924</v>
+        <v>2.2808</v>
       </c>
       <c r="E18" t="n">
-        <v>1.133</v>
+        <v>1.8461</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6593</v>
+        <v>0.4347</v>
       </c>
       <c r="G18" t="n">
         <v>3.283</v>
@@ -1858,13 +1858,13 @@
         <v>0.5947</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3628</v>
+        <v>0.1257</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1745</v>
+        <v>-0.4614</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8117</v>
+        <v>0.5871</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5331</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6914</v>
+        <v>1.6313</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6804</v>
+        <v>-1.1897</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3718</v>
+        <v>2.821</v>
       </c>
       <c r="G19" t="n">
         <v>2.9698</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6263</v>
+        <v>0.5662</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2975</v>
+        <v>-0.2118</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3288</v>
+        <v>0.7781</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1207</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4993</v>
+        <v>0.9172</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6797</v>
+        <v>-1.3741</v>
       </c>
       <c r="F20" t="n">
-        <v>2.179</v>
+        <v>2.2913</v>
       </c>
       <c r="G20" t="n">
         <v>0.4687</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.384</v>
+        <v>0.034</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8001</v>
+        <v>-0.4945</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4162</v>
+        <v>0.5285</v>
       </c>
       <c r="V20" t="n">
         <v>0.2163</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0863</v>
+        <v>-0.0374</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0931</v>
+        <v>-3.2968</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0068</v>
+        <v>3.2595</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7619</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1949</v>
+        <v>-0.1459</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6312</v>
+        <v>-0.835</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4363</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1207</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7167</v>
+        <v>-1.2084</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5012</v>
+        <v>-0.9087</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2155</v>
+        <v>-0.2997</v>
       </c>
       <c r="G22" t="n">
         <v>0.07000000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0062</v>
+        <v>-0.4855</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4295</v>
+        <v>0.0221</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4233</v>
+        <v>-0.5075</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8173</v>
+        <v>-1.4451</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0167</v>
+        <v>0.2204</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8341</v>
+        <v>-1.6656</v>
       </c>
       <c r="G23" t="n">
         <v>1.2715</v>
@@ -2248,13 +2248,13 @@
         <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1394</v>
+        <v>-0.7672</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5616</v>
+        <v>-0.3578</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5778</v>
+        <v>-0.4094</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1476</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.7775</v>
+        <v>16.7773</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2918000000000009</v>
+        <v>0.2918000000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>16.4855</v>
+        <v>16.48559999999999</v>
       </c>
       <c r="G24" t="n">
         <v>14.4026</v>
@@ -2326,7 +2326,7 @@
         <v>11.8935</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5688000000000004</v>
+        <v>0.5688000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-3.8713</v>
